--- a/ehdidata_2007to2022_published20250226_description.xlsx
+++ b/ehdidata_2007to2022_published20250226_description.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chaitan\Box\CPHSS\EHDI Seeser\Data\website_ready_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AA5C07-1B08-489A-91AA-3F926FDE3C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5347CDFF-C2C2-4FF6-B202-F4A349E8F35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12132" yWindow="0" windowWidth="10908" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_description" sheetId="1" r:id="rId1"/>
@@ -502,9 +502,6 @@
     <t>Percentage of babies with documented loss to follow-up out of those who did not pass their final/most recent screening test</t>
   </si>
   <si>
-    <t>Percentage of babies diagnosed with either hearing loss or no hearing loss out of those tho did not pass their last/final screening</t>
-  </si>
-  <si>
     <t>Percentage of babies diagnosed with hearing loss before 3 months of age out of total with hearing loss</t>
   </si>
   <si>
@@ -923,6 +920,9 @@
   </si>
   <si>
     <t>PerReferStDia</t>
+  </si>
+  <si>
+    <t>Percentage of babies diagnosed with either hearing loss or no hearing loss out of those who did not pass their last/final screening</t>
   </si>
 </sst>
 </file>
@@ -1585,7 +1585,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="9" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
@@ -1599,7 +1599,7 @@
         <v>96</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E2" s="1"/>
     </row>
@@ -1611,10 +1611,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -1626,30 +1626,30 @@
         <v>39</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1660,13 +1660,13 @@
         <v>49</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -1677,13 +1677,13 @@
         <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="9" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
@@ -1694,13 +1694,13 @@
         <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1711,13 +1711,13 @@
         <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>119</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -1728,13 +1728,13 @@
         <v>60</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -1745,13 +1745,13 @@
         <v>63</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1765,10 +1765,10 @@
         <v>147</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1782,78 +1782,78 @@
         <v>148</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="E17" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1870,7 +1870,7 @@
         <v>121</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1878,7 +1878,7 @@
         <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>150</v>
@@ -1887,15 +1887,15 @@
         <v>120</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>151</v>
@@ -1904,7 +1904,7 @@
         <v>122</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1921,7 +1921,7 @@
         <v>123</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1938,7 +1938,7 @@
         <v>124</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1955,7 +1955,7 @@
         <v>127</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1965,14 +1965,14 @@
       <c r="B24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>155</v>
+      <c r="C24" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -1989,7 +1989,7 @@
         <v>125</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -2000,13 +2000,13 @@
         <v>38</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>126</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2017,13 +2017,13 @@
         <v>36</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>106</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2034,52 +2034,52 @@
         <v>37</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>107</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" spans="1:5" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
         <v>283</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>284</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>42</v>
@@ -2091,24 +2091,24 @@
         <v>128</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="9" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>62</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -2125,7 +2125,7 @@
         <v>129</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:5" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
@@ -2142,7 +2142,7 @@
         <v>105</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:5" s="9" customFormat="1" ht="72" x14ac:dyDescent="0.3">
@@ -2159,24 +2159,24 @@
         <v>130</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="9" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="9" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37" spans="1:5" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -2190,10 +2190,10 @@
         <v>136</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:5" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -2207,10 +2207,10 @@
         <v>137</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -2221,13 +2221,13 @@
         <v>28</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>131</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2238,13 +2238,13 @@
         <v>30</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>132</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2255,16 +2255,16 @@
         <v>27</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>133</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
@@ -2272,13 +2272,13 @@
         <v>7</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>134</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:5" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -2289,13 +2289,13 @@
         <v>9</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>135</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2306,13 +2306,13 @@
         <v>13</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>104</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="45" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2323,13 +2323,13 @@
         <v>15</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>103</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="46" spans="1:5" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -2340,13 +2340,13 @@
         <v>11</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>102</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="47" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2357,13 +2357,13 @@
         <v>18</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="48" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2374,13 +2374,13 @@
         <v>20</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2391,13 +2391,13 @@
         <v>16</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:5" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -2408,13 +2408,13 @@
         <v>21</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -2425,13 +2425,13 @@
         <v>29</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -2442,47 +2442,47 @@
         <v>94</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="D53" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="D53" s="8" t="s">
-        <v>225</v>
-      </c>
       <c r="E53" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="D54" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="D54" s="8" t="s">
-        <v>229</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -2493,13 +2493,13 @@
         <v>40</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2507,33 +2507,33 @@
         <v>80</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>97</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2544,13 +2544,13 @@
         <v>57</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>58</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2561,13 +2561,13 @@
         <v>31</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -2578,30 +2578,30 @@
         <v>26</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2618,7 +2618,7 @@
         <v>110</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2629,16 +2629,16 @@
         <v>22</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>111</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="13" t="s">
         <v>145</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>112</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -2669,7 +2669,7 @@
         <v>113</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
